--- a/data/trans_orig/P35_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64527</t>
+          <t>60789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22597</t>
+          <t>23633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>53336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51077</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98522</t>
+          <t>98821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56913</t>
+          <t>57872</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79903</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>312679</t>
+          <t>314622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>362049</t>
+          <t>360884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204637</t>
+          <t>206468</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246688</t>
+          <t>246135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>535489</t>
+          <t>536008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>597381</t>
+          <t>599075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>52862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>52061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52032</t>
+          <t>52396</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>93772</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24079</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>19497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>35003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77809</t>
+          <t>75610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80235</t>
+          <t>81563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87756</t>
+          <t>85827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145030</t>
+          <t>143851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>296645</t>
+          <t>292601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>342388</t>
+          <t>339267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>377630</t>
+          <t>377236</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>444961</t>
+          <t>443255</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>688435</t>
+          <t>688805</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>770485</t>
+          <t>775332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55308</t>
+          <t>55463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51333</t>
+          <t>51456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65798</t>
+          <t>66635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99314</t>
+          <t>98812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36551</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>70770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104096</t>
+          <t>106755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102352</t>
+          <t>101266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133216</t>
+          <t>132903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180195</t>
+          <t>178706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226750</t>
+          <t>225161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>377899</t>
+          <t>378257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419312</t>
+          <t>419772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>349653</t>
+          <t>350932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>385995</t>
+          <t>386306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>737243</t>
+          <t>739885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>791906</t>
+          <t>793184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31603</t>
+          <t>31612</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44028</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100183</t>
+          <t>104228</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32956</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53915</t>
+          <t>53443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73864</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>232620</t>
+          <t>231769</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>163873</t>
+          <t>168262</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>217136</t>
+          <t>218883</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>206737</t>
+          <t>223561</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>435356</t>
+          <t>433338</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>573719</t>
+          <t>574208</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>792190</t>
+          <t>794549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>433231</t>
+          <t>430725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>496864</t>
+          <t>491263</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1024273</t>
+          <t>1025984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1326228</t>
+          <t>1306809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31459</t>
+          <t>30637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>55353</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47172</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66958</t>
+          <t>68013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97169</t>
+          <t>98013</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>28112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>34094</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>35963</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56772</t>
+          <t>57438</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>164420</t>
+          <t>165402</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206790</t>
+          <t>206847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>161740</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>193635</t>
+          <t>193560</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>335684</t>
+          <t>335592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>389216</t>
+          <t>388540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>290038</t>
+          <t>291741</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>337894</t>
+          <t>335848</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>286241</t>
+          <t>286472</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>320954</t>
+          <t>319653</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>588335</t>
+          <t>589052</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>644079</t>
+          <t>645914</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40292</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48574</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>83334</t>
+          <t>80633</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>124269</t>
+          <t>124943</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>154554</t>
+          <t>154766</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>233464</t>
+          <t>232871</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>155899</t>
+          <t>155705</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>376161</t>
+          <t>376452</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>170580</t>
+          <t>170995</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>203433</t>
+          <t>202744</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>313718</t>
+          <t>314084</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>529127</t>
+          <t>532668</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>495093</t>
+          <t>495185</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>770850</t>
+          <t>773884</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45827</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>66844</t>
+          <t>67379</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>104575</t>
+          <t>103054</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>129623</t>
+          <t>128873</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>151186</t>
+          <t>151847</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>178745</t>
+          <t>180253</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>262051</t>
+          <t>263825</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>300516</t>
+          <t>302772</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>123643</t>
+          <t>123638</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>150403</t>
+          <t>151590</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>202271</t>
+          <t>202112</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>230374</t>
+          <t>231001</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>335098</t>
+          <t>333236</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>374456</t>
+          <t>372678</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>197361</t>
+          <t>190888</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>291370</t>
+          <t>290477</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>204602</t>
+          <t>206715</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>286856</t>
+          <t>287427</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>431360</t>
+          <t>436537</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>558136</t>
+          <t>561352</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>63014</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>84247</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>125935</t>
+          <t>126208</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>155565</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>218111</t>
+          <t>217810</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>596184</t>
+          <t>587059</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>838612</t>
+          <t>837186</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>748005</t>
+          <t>716102</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>980549</t>
+          <t>983232</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1442636</t>
+          <t>1458872</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1778575</t>
+          <t>1787915</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2254994</t>
+          <t>2261121</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2597568</t>
+          <t>2616493</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2294154</t>
+          <t>2285001</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2612763</t>
+          <t>2650351</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4606494</t>
+          <t>4585586</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5082941</t>
+          <t>5067105</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37686</t>
+          <t>39253</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21017</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60789</t>
+          <t>62046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>45657</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23633</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>65971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73431</t>
+          <t>84910</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>64258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98821</t>
+          <t>117283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15597</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57872</t>
+          <t>64438</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>62625</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37200</t>
+          <t>42067</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79714</t>
+          <t>86733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>340938</t>
+          <t>341944</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>314622</t>
+          <t>313039</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>360884</t>
+          <t>361371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>227664</t>
+          <t>262598</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206468</t>
+          <t>236062</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246135</t>
+          <t>285011</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>568602</t>
+          <t>604542</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>536008</t>
+          <t>571997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>599075</t>
+          <t>634769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34836</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52862</t>
+          <t>62685</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37557</t>
+          <t>46111</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>33950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>60888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>72393</t>
+          <t>86953</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52396</t>
+          <t>69041</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>96099</t>
+          <t>111442</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13238</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>27974</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>41063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55606</t>
+          <t>62831</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39750</t>
+          <t>45039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75610</t>
+          <t>83062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61296</t>
+          <t>65645</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>51190</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81563</t>
+          <t>82440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>116902</t>
+          <t>128476</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85827</t>
+          <t>106108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143851</t>
+          <t>154410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>319867</t>
+          <t>356666</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>292601</t>
+          <t>328566</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>339267</t>
+          <t>379055</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>403063</t>
+          <t>377905</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>377236</t>
+          <t>358056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>443255</t>
+          <t>397861</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>722930</t>
+          <t>734571</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>688805</t>
+          <t>700992</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>775332</t>
+          <t>762657</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41355</t>
+          <t>50231</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55463</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39425</t>
+          <t>46038</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51456</t>
+          <t>58292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>80779</t>
+          <t>96269</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66635</t>
+          <t>77972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98812</t>
+          <t>114435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>28708</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86512</t>
+          <t>98740</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70770</t>
+          <t>79034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106755</t>
+          <t>119435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>117040</t>
+          <t>134983</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101266</t>
+          <t>119739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132903</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,27 +2159,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>203552</t>
+          <t>233723</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178706</t>
+          <t>209519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225161</t>
+          <t>259501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>398624</t>
+          <t>459397</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>378257</t>
+          <t>437511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419772</t>
+          <t>483931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>367890</t>
+          <t>419318</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350932</t>
+          <t>399704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>386306</t>
+          <t>439935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>766514</t>
+          <t>878715</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>739885</t>
+          <t>848924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>793184</t>
+          <t>907379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>541177</t>
+          <t>620790</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>541177</t>
+          <t>620790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>541177</t>
+          <t>620790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1077515</t>
+          <t>1241627</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1077515</t>
+          <t>1241627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1077515</t>
+          <t>1241627</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>33347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60098</t>
+          <t>61125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40789</t>
+          <t>47374</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31612</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52026</t>
+          <t>58813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>79022</t>
+          <t>92657</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46634</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>112568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19041</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>33097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53443</t>
+          <t>58645</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>159416</t>
+          <t>174199</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68139</t>
+          <t>152377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>231769</t>
+          <t>198296</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>195157</t>
+          <t>207394</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>168262</t>
+          <t>188627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>218883</t>
+          <t>226193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>354573</t>
+          <t>381593</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>223561</t>
+          <t>355005</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>433338</t>
+          <t>415114</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>670434</t>
+          <t>459286</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>574208</t>
+          <t>434121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>794549</t>
+          <t>485303</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>456781</t>
+          <t>459062</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>430725</t>
+          <t>438725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>491263</t>
+          <t>478444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1127215</t>
+          <t>918348</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1025984</t>
+          <t>885445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1306809</t>
+          <t>947213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711768</t>
+          <t>735773</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711768</t>
+          <t>735773</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711768</t>
+          <t>735773</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1599554</t>
+          <t>1436390</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1599554</t>
+          <t>1436390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1599554</t>
+          <t>1436390</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,17 +3001,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30637</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55353</t>
+          <t>60568</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>42488</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47797</t>
+          <t>52612</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>81302</t>
+          <t>89157</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>68013</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98013</t>
+          <t>107075</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>32381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26117</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34094</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>51796</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35963</t>
+          <t>41337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>64962</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>184912</t>
+          <t>199376</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>165402</t>
+          <t>178281</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206847</t>
+          <t>224744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>177247</t>
+          <t>200071</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161740</t>
+          <t>182359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>193560</t>
+          <t>218705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>362159</t>
+          <t>399447</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>335592</t>
+          <t>371232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>388540</t>
+          <t>427188</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>314293</t>
+          <t>340766</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>291741</t>
+          <t>317712</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>335848</t>
+          <t>363758</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>335952</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>286472</t>
+          <t>315579</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>319653</t>
+          <t>357244</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>617827</t>
+          <t>676718</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>589052</t>
+          <t>646481</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>645914</t>
+          <t>707892</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545218</t>
+          <t>607772</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545218</t>
+          <t>607772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545218</t>
+          <t>607772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1106452</t>
+          <t>1217118</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1106452</t>
+          <t>1217118</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1106452</t>
+          <t>1217118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>26535</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40292</t>
+          <t>46382</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>33314</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49503</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>61084</t>
+          <t>68585</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31711</t>
+          <t>57178</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>80633</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>23870</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>139389</t>
+          <t>150451</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>124943</t>
+          <t>134790</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>154766</t>
+          <t>167208</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>150469</t>
+          <t>165395</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>60483</t>
+          <t>150615</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>232871</t>
+          <t>182096</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>289858</t>
+          <t>315846</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>155705</t>
+          <t>294527</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>376452</t>
+          <t>340925</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>186908</t>
+          <t>209218</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>170995</t>
+          <t>192093</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>202744</t>
+          <t>227511</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>416702</t>
+          <t>228114</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>314084</t>
+          <t>211127</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>532668</t>
+          <t>242499</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>603609</t>
+          <t>437331</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>495185</t>
+          <t>410594</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>773884</t>
+          <t>457001</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>975991</t>
+          <t>845633</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>975991</t>
+          <t>845633</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>975991</t>
+          <t>845633</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>37358</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>24012</t>
+          <t>26713</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>55575</t>
+          <t>61606</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>50205</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>67379</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,27 +4322,27 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>19882</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>26999</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>116167</t>
+          <t>126368</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>103054</t>
+          <t>112348</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>128873</t>
+          <t>140454</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>164661</t>
+          <t>181005</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>151847</t>
+          <t>165528</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>180253</t>
+          <t>195592</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>280828</t>
+          <t>307373</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>263825</t>
+          <t>283800</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>302772</t>
+          <t>326859</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>137091</t>
+          <t>150914</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>123638</t>
+          <t>136735</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>151590</t>
+          <t>165553</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>216851</t>
+          <t>234624</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>202112</t>
+          <t>220422</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>231001</t>
+          <t>249684</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>353942</t>
+          <t>385538</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>333236</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>372678</t>
+          <t>409682</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425427</t>
+          <t>464200</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425427</t>
+          <t>464200</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425427</t>
+          <t>464200</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708186</t>
+          <t>774398</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708186</t>
+          <t>774398</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708186</t>
+          <t>774398</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>250784</t>
+          <t>285161</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>190888</t>
+          <t>250295</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>290477</t>
+          <t>324539</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>252802</t>
+          <t>294975</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>206715</t>
+          <t>261820</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>287427</t>
+          <t>326249</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>503586</t>
+          <t>580135</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>436537</t>
+          <t>535725</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>561352</t>
+          <t>636233</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>82969</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>63014</t>
+          <t>81195</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>103445</t>
+          <t>121037</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>105312</t>
+          <t>120063</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>82936</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>126208</t>
+          <t>140616</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>188281</t>
+          <t>218463</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>156361</t>
+          <t>191229</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>217810</t>
+          <t>245245</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>757910</t>
+          <t>831009</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>587059</t>
+          <t>781410</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>837186</t>
+          <t>883940</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>905520</t>
+          <t>998074</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>716102</t>
+          <t>955359</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>983232</t>
+          <t>1046008</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1663430</t>
+          <t>1829083</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1458872</t>
+          <t>1760189</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1787915</t>
+          <t>1898049</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2368154</t>
+          <t>2318192</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2261121</t>
+          <t>2253048</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2616493</t>
+          <t>2378110</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2392485</t>
+          <t>2317572</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2285001</t>
+          <t>2262407</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2650351</t>
+          <t>2366738</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4760640</t>
+          <t>4635764</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4585586</t>
+          <t>4546423</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5067105</t>
+          <t>4708190</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
